--- a/results/feature_selection/global/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/qP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -483,253 +488,274 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S, V, P, T, I, dXdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>T, I, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9615396107329776</v>
+        <v>0.5115484172639022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005132740327156671</v>
+        <v>0.001085217281506565</v>
       </c>
       <c r="F2" t="n">
-        <v>8.194118400616678e-07</v>
+        <v>1.040662920523284e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009052136985605487</v>
+        <v>0.003225930750222769</v>
       </c>
       <c r="H2" t="n">
-        <v>317.8167210874403</v>
+        <v>355.6428642034781</v>
       </c>
       <c r="I2" t="n">
-        <v>-1727.820198760923</v>
+        <v>0.149042759461273</v>
       </c>
       <c r="J2" t="n">
-        <v>-1713.718790932898</v>
+        <v>-1412.660373881818</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1398.558966053793</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S, V, P, T, I, dXdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.961273394502693</v>
+        <v>0.269548466885587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004906886211898644</v>
+        <v>0.002049467372194879</v>
       </c>
       <c r="F3" t="n">
-        <v>8.250836685394597e-07</v>
+        <v>1.556252149892723e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009083411630766601</v>
+        <v>0.003944936184392242</v>
       </c>
       <c r="H3" t="n">
-        <v>278.8990669220338</v>
+        <v>408.7377843905917</v>
       </c>
       <c r="I3" t="n">
-        <v>-1728.964848878478</v>
+        <v>0.2206463536993732</v>
       </c>
       <c r="J3" t="n">
-        <v>-1717.683722616057</v>
+        <v>-1366.759980283108</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1358.299135586293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V, P, I, Plag1</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8118122762719563</v>
+        <v>0.2677302896783095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008769491858705674</v>
+        <v>0.002031067717314762</v>
       </c>
       <c r="F4" t="n">
-        <v>4.009404270622743e-06</v>
+        <v>1.560125839055434e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002002349687397969</v>
+        <v>0.003949842831120542</v>
       </c>
       <c r="H4" t="n">
-        <v>980.9837827980131</v>
+        <v>420.8667356850953</v>
       </c>
       <c r="I4" t="n">
-        <v>-1512.931618189379</v>
+        <v>0.2211918339773806</v>
       </c>
       <c r="J4" t="n">
-        <v>-1473.447676270909</v>
+        <v>-1366.451713631717</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1357.990868934902</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7999707516657671</v>
+        <v>0.2321486523529487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008990698253493507</v>
+        <v>0.001883244988304854</v>
       </c>
       <c r="F5" t="n">
-        <v>4.261692030877233e-06</v>
+        <v>1.635933742898416e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002064386599180791</v>
+        <v>0.004044667777331552</v>
       </c>
       <c r="H5" t="n">
-        <v>767.9330127488605</v>
+        <v>529.3734326606921</v>
       </c>
       <c r="I5" t="n">
-        <v>-1531.364691488233</v>
+        <v>0.2318668558303157</v>
       </c>
       <c r="J5" t="n">
-        <v>-1528.544409922628</v>
+        <v>-1360.56825415552</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1352.107409458705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S, P, T, mu, dXdt, mu_calc, dXdt_calc</t>
+          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7551500432307339</v>
+        <v>0.03339126656543834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001185582608657773</v>
+        <v>0.001506761410443362</v>
       </c>
       <c r="F6" t="n">
-        <v>5.216612661467654e-06</v>
+        <v>2.059393199024194e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00228399051256078</v>
+        <v>0.004538053766786148</v>
       </c>
       <c r="H6" t="n">
-        <v>1545.975310490955</v>
+        <v>912.854054227928</v>
       </c>
       <c r="I6" t="n">
-        <v>-1486.294122984631</v>
+        <v>0.2924970357827618</v>
       </c>
       <c r="J6" t="n">
-        <v>-1455.271025762976</v>
+        <v>-1328.023747053558</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1313.922339225533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T, mu, dVdt, Plag1, X_calc, dXdt_calc</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7124350293656394</v>
+        <v>-0.004706728020200446</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000846492971645414</v>
+        <v>0.0019397778233643</v>
       </c>
       <c r="F7" t="n">
-        <v>6.126670743991228e-06</v>
+        <v>2.140562288679886e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002475211252396697</v>
+        <v>0.004626621109059923</v>
       </c>
       <c r="H7" t="n">
-        <v>526.7594558520766</v>
+        <v>2079.640232996471</v>
       </c>
       <c r="I7" t="n">
-        <v>-1466.354523960863</v>
+        <v>0.6038540046841619</v>
       </c>
       <c r="J7" t="n">
-        <v>-1435.331426739208</v>
+        <v>-1331.23025792253</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1328.409976356925</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>X, V, P, dXdt, dVdt, Xlag1, Plag1, X_calc, V_calc</t>
+          <t>T, X_calc, V_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.6220878234901008</v>
+        <v>-0.2838996050589189</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005287528177415964</v>
+        <v>0.0040302612674729</v>
       </c>
       <c r="F8" t="n">
-        <v>3.455913976740021e-05</v>
+        <v>2.735392329317482e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005878702217955951</v>
+        <v>0.005230097828260463</v>
       </c>
       <c r="H8" t="n">
-        <v>3952.179349922617</v>
+        <v>1702.23606096704</v>
       </c>
       <c r="I8" t="n">
-        <v>-1255.831974660645</v>
+        <v>0.7753780585279619</v>
       </c>
       <c r="J8" t="n">
-        <v>-1230.4494405702</v>
+        <v>-1292.824673375244</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1278.723265547219</v>
       </c>
     </row>
     <row r="9">
@@ -739,69 +765,75 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V, P, dVdt, Plag1</t>
+          <t>T, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8105902278785209</v>
+        <v>-0.6063606228246397</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005780261349593877</v>
+        <v>0.004709205173026094</v>
       </c>
       <c r="F9" t="n">
-        <v>3.857524841787622e-05</v>
+        <v>3.422406634037813e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006210897553323209</v>
+        <v>0.005850133873714184</v>
       </c>
       <c r="H9" t="n">
-        <v>3884.605960213069</v>
+        <v>1841.687773142155</v>
       </c>
       <c r="I9" t="n">
-        <v>-1252.199565263708</v>
+        <v>0.9698642873876604</v>
       </c>
       <c r="J9" t="n">
-        <v>-1240.918439001288</v>
+        <v>-1263.040101933948</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1246.118412540318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>X, S, V, P, T, I, mu, dXdt, dSdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>I, X_calc, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.537266744642415</v>
+        <v>-0.8216616894928972</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008468832570964554</v>
+        <v>0.005184912806866946</v>
       </c>
       <c r="F10" t="n">
-        <v>7.536268631845752e-05</v>
+        <v>3.881112972086103e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008681168488081401</v>
+        <v>0.006229857921402464</v>
       </c>
       <c r="H10" t="n">
-        <v>4472.862257525736</v>
+        <v>2530.105081598282</v>
       </c>
       <c r="I10" t="n">
-        <v>-1143.156586950037</v>
+        <v>1.098051349277348</v>
       </c>
       <c r="J10" t="n">
-        <v>-1095.211800334752</v>
+        <v>-1249.443634495058</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1235.342226667033</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/qP/metrics_global.xlsx
@@ -500,28 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5115484172639022</v>
+        <v>0.5095255802797782</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001085217281506565</v>
+        <v>0.001102750399317309</v>
       </c>
       <c r="F2" t="n">
-        <v>1.040662920523284e-05</v>
+        <v>1.028749743765325e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003225930750222769</v>
+        <v>0.003207412888552587</v>
       </c>
       <c r="H2" t="n">
-        <v>355.6428642034781</v>
+        <v>375.8987397096124</v>
       </c>
       <c r="I2" t="n">
-        <v>0.149042759461273</v>
+        <v>0.1496495271642729</v>
       </c>
       <c r="J2" t="n">
-        <v>-1412.660373881818</v>
+        <v>-1437.0572363704</v>
       </c>
       <c r="K2" t="n">
-        <v>-1398.558966053793</v>
+        <v>-1422.875826835643</v>
       </c>
     </row>
     <row r="3">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.269548466885587</v>
+        <v>0.2660437790386159</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002049467372194879</v>
+        <v>0.002037764806441125</v>
       </c>
       <c r="F3" t="n">
-        <v>1.556252149892723e-05</v>
+        <v>1.53944271890814e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003944936184392242</v>
+        <v>0.003923573267963961</v>
       </c>
       <c r="H3" t="n">
-        <v>408.7377843905917</v>
+        <v>431.0123175631525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2206463536993732</v>
+        <v>0.2216976423874476</v>
       </c>
       <c r="J3" t="n">
-        <v>-1366.759980283108</v>
+        <v>-1390.269628094201</v>
       </c>
       <c r="K3" t="n">
-        <v>-1358.299135586293</v>
+        <v>-1381.760782373347</v>
       </c>
     </row>
     <row r="4">
@@ -578,28 +578,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2677302896783095</v>
+        <v>0.2639917366450426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002031067717314762</v>
+        <v>0.002018962947163218</v>
       </c>
       <c r="F4" t="n">
-        <v>1.560125839055434e-05</v>
+        <v>1.543746792681831e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003949842831120542</v>
+        <v>0.003929054329837946</v>
       </c>
       <c r="H4" t="n">
-        <v>420.8667356850953</v>
+        <v>442.1060209155689</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2211918339773806</v>
+        <v>0.222313285234036</v>
       </c>
       <c r="J4" t="n">
-        <v>-1366.451713631717</v>
+        <v>-1389.917840670349</v>
       </c>
       <c r="K4" t="n">
-        <v>-1357.990868934902</v>
+        <v>-1381.408994949494</v>
       </c>
     </row>
     <row r="5">
@@ -617,28 +617,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2321486523529487</v>
+        <v>0.2258213546397064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001883244988304854</v>
+        <v>0.001866882249816778</v>
       </c>
       <c r="F5" t="n">
-        <v>1.635933742898416e-05</v>
+        <v>1.623807585107689e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004044667777331552</v>
+        <v>0.004029649594080966</v>
       </c>
       <c r="H5" t="n">
-        <v>529.3734326606921</v>
+        <v>540.1649056515072</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2318668558303157</v>
+        <v>0.2337649602611839</v>
       </c>
       <c r="J5" t="n">
-        <v>-1360.56825415552</v>
+        <v>-1383.547115753182</v>
       </c>
       <c r="K5" t="n">
-        <v>-1352.107409458705</v>
+        <v>-1375.038270032328</v>
       </c>
     </row>
     <row r="6">
@@ -648,36 +648,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>T, V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.03339126656543834</v>
+        <v>0.09681663107629146</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001506761410443362</v>
+        <v>0.001390174728782252</v>
       </c>
       <c r="F6" t="n">
-        <v>2.059393199024194e-05</v>
+        <v>1.894389639898809e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004538053766786148</v>
+        <v>0.004352458661376129</v>
       </c>
       <c r="H6" t="n">
-        <v>912.854054227928</v>
+        <v>905.0098481078604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2924970357827618</v>
+        <v>0.2729682714045919</v>
       </c>
       <c r="J6" t="n">
-        <v>-1328.023747053558</v>
+        <v>-1362.127624778212</v>
       </c>
       <c r="K6" t="n">
-        <v>-1313.922339225533</v>
+        <v>-1350.782497150406</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.004706728020200446</v>
+        <v>-0.004140114639367365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0019397778233643</v>
+        <v>0.001928194465336112</v>
       </c>
       <c r="F7" t="n">
-        <v>2.140562288679886e-05</v>
+        <v>2.106142224968605e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004626621109059923</v>
+        <v>0.004589272518568281</v>
       </c>
       <c r="H7" t="n">
-        <v>2079.640232996471</v>
+        <v>1972.72263353067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6038540046841619</v>
+        <v>0.6035135547747701</v>
       </c>
       <c r="J7" t="n">
-        <v>-1331.23025792253</v>
+        <v>-1354.776507559721</v>
       </c>
       <c r="K7" t="n">
-        <v>-1328.409976356925</v>
+        <v>-1351.94022565277</v>
       </c>
     </row>
     <row r="8">
@@ -730,32 +730,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, dVdt_calc, Xlag1_calc</t>
+          <t>T, X_calc, V_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.2838996050589189</v>
+        <v>-0.4240958666406447</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0040302612674729</v>
+        <v>0.004252413252942097</v>
       </c>
       <c r="F8" t="n">
-        <v>2.735392329317482e-05</v>
+        <v>2.986981989273802e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005230097828260463</v>
+        <v>0.00546532889154331</v>
       </c>
       <c r="H8" t="n">
-        <v>1702.23606096704</v>
+        <v>1365.434986724613</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7753780585279619</v>
+        <v>0.8594993377322367</v>
       </c>
       <c r="J8" t="n">
-        <v>-1292.824673375244</v>
+        <v>-1302.751406387777</v>
       </c>
       <c r="K8" t="n">
-        <v>-1278.723265547219</v>
+        <v>-1288.56999685302</v>
       </c>
     </row>
     <row r="9">
@@ -765,36 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>V_calc, mu_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.6063606228246397</v>
+        <v>-0.7635629573508735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004709205173026094</v>
+        <v>0.005089381444717056</v>
       </c>
       <c r="F9" t="n">
-        <v>3.422406634037813e-05</v>
+        <v>3.699000126293294e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005850133873714184</v>
+        <v>0.006081940583640467</v>
       </c>
       <c r="H9" t="n">
-        <v>1841.687773142155</v>
+        <v>2533.633433102007</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9698642873876604</v>
+        <v>1.061189560412292</v>
       </c>
       <c r="J9" t="n">
-        <v>-1263.040101933948</v>
+        <v>-1279.812727665148</v>
       </c>
       <c r="K9" t="n">
-        <v>-1246.118412540318</v>
+        <v>-1271.303881944293</v>
       </c>
     </row>
     <row r="10">
@@ -812,28 +812,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.8216616894928972</v>
+        <v>-0.8199159914848282</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005184912806866946</v>
+        <v>0.005171315006113971</v>
       </c>
       <c r="F10" t="n">
-        <v>3.881112972086103e-05</v>
+        <v>3.817198277093439e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006229857921402464</v>
+        <v>0.006178347899797679</v>
       </c>
       <c r="H10" t="n">
-        <v>2530.105081598282</v>
+        <v>2550.0729112243</v>
       </c>
       <c r="I10" t="n">
-        <v>1.098051349277348</v>
+        <v>1.097003035666776</v>
       </c>
       <c r="J10" t="n">
-        <v>-1249.443634495058</v>
+        <v>-1271.849502092121</v>
       </c>
       <c r="K10" t="n">
-        <v>-1235.342226667033</v>
+        <v>-1257.668092557363</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/qP/metrics_global.xlsx
@@ -488,157 +488,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, I, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, I, Plag1, X_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5095255802797782</v>
+        <v>0.9655218740899651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001102750399317309</v>
+        <v>0.0004287143115979861</v>
       </c>
       <c r="F2" t="n">
-        <v>1.028749743765325e-05</v>
+        <v>7.345683476491423e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003207412888552587</v>
+        <v>0.0008570696282386526</v>
       </c>
       <c r="H2" t="n">
-        <v>375.8987397096124</v>
+        <v>179.2981137941709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1496495271642729</v>
+        <v>0.01334395197085381</v>
       </c>
       <c r="J2" t="n">
-        <v>-1437.0572363704</v>
+        <v>-1739.373866252798</v>
       </c>
       <c r="K2" t="n">
-        <v>-1422.875826835643</v>
+        <v>-1722.452176859167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, T, I, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2660437790386159</v>
+        <v>0.9642833025630682</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002037764806441125</v>
+        <v>0.0004405533831163183</v>
       </c>
       <c r="F3" t="n">
-        <v>1.53944271890814e-05</v>
+        <v>7.609565406249453e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003923573267963961</v>
+        <v>0.0008723282298681759</v>
       </c>
       <c r="H3" t="n">
-        <v>431.0123175631525</v>
+        <v>213.9112714998324</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2216976423874476</v>
+        <v>0.01271554190065799</v>
       </c>
       <c r="J3" t="n">
-        <v>-1390.269628094201</v>
+        <v>-1738.997509031197</v>
       </c>
       <c r="K3" t="n">
-        <v>-1381.760782373347</v>
+        <v>-1727.716382768777</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, I, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2639917366450426</v>
+        <v>0.8088953723726542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002018962947163218</v>
+        <v>0.0008712023880235329</v>
       </c>
       <c r="F4" t="n">
-        <v>1.543746792681831e-05</v>
+        <v>4.071549912852621e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003929054329837946</v>
+        <v>0.002017808195258563</v>
       </c>
       <c r="H4" t="n">
-        <v>442.1060209155689</v>
+        <v>1011.801747519163</v>
       </c>
       <c r="I4" t="n">
-        <v>0.222313285234036</v>
+        <v>0.05933423837314275</v>
       </c>
       <c r="J4" t="n">
-        <v>-1389.917840670349</v>
+        <v>-1531.024365312006</v>
       </c>
       <c r="K4" t="n">
-        <v>-1381.408994949494</v>
+        <v>-1519.743239049585</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2258213546397064</v>
+        <v>0.7999707516657673</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001866882249816778</v>
+        <v>0.0008990698253493507</v>
       </c>
       <c r="F5" t="n">
-        <v>1.623807585107689e-05</v>
+        <v>4.261692030877233e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004029649594080966</v>
+        <v>0.002064386599180791</v>
       </c>
       <c r="H5" t="n">
-        <v>540.1649056515072</v>
+        <v>767.9330127488605</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2337649602611839</v>
+        <v>0.06051175768469145</v>
       </c>
       <c r="J5" t="n">
-        <v>-1383.547115753182</v>
+        <v>-1531.364691488234</v>
       </c>
       <c r="K5" t="n">
-        <v>-1375.038270032328</v>
+        <v>-1528.544409922629</v>
       </c>
     </row>
     <row r="6">
@@ -648,36 +648,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09681663107629146</v>
+        <v>0.7760657642497533</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001390174728782252</v>
+        <v>0.0009036708302509669</v>
       </c>
       <c r="F6" t="n">
-        <v>1.894389639898809e-05</v>
+        <v>4.770996021255786e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004352458661376129</v>
+        <v>0.002184260978284368</v>
       </c>
       <c r="H6" t="n">
-        <v>905.0098481078604</v>
+        <v>665.3928638920125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2729682714045919</v>
+        <v>0.0676836104222889</v>
       </c>
       <c r="J6" t="n">
-        <v>-1362.127624778212</v>
+        <v>-1517.366477706389</v>
       </c>
       <c r="K6" t="n">
-        <v>-1350.782497150406</v>
+        <v>-1514.546196140784</v>
       </c>
     </row>
     <row r="7">
@@ -687,75 +687,75 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>P, T, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.004140114639367365</v>
+        <v>0.7550052117256926</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001928194465336112</v>
+        <v>0.001203059008018534</v>
       </c>
       <c r="F7" t="n">
-        <v>2.106142224968605e-05</v>
+        <v>5.21969834656618e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004589272518568281</v>
+        <v>0.002284665915744834</v>
       </c>
       <c r="H7" t="n">
-        <v>1972.72263353067</v>
+        <v>1597.370159368248</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6035135547747701</v>
+        <v>0.07500209027113483</v>
       </c>
       <c r="J7" t="n">
-        <v>-1354.776507559721</v>
+        <v>-1502.220797273454</v>
       </c>
       <c r="K7" t="n">
-        <v>-1351.94022565277</v>
+        <v>-1493.759952576639</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.4240958666406447</v>
+        <v>-0.7546567178198615</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004252413252942097</v>
+        <v>0.005656028731159132</v>
       </c>
       <c r="F8" t="n">
-        <v>2.986981989273802e-05</v>
+        <v>3.738356572116539e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00546532889154331</v>
+        <v>0.0061142101469581</v>
       </c>
       <c r="H8" t="n">
-        <v>1365.434986724613</v>
+        <v>4087.147715952747</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8594993377322367</v>
+        <v>1.055846367683926</v>
       </c>
       <c r="J8" t="n">
-        <v>-1302.751406387777</v>
+        <v>-1258.090641797773</v>
       </c>
       <c r="K8" t="n">
-        <v>-1288.56999685302</v>
+        <v>-1249.629797100958</v>
       </c>
     </row>
     <row r="9">
@@ -765,75 +765,75 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7635629573508735</v>
+        <v>-0.8710860163366305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005089381444717056</v>
+        <v>0.005909582879450621</v>
       </c>
       <c r="F9" t="n">
-        <v>3.699000126293294e-05</v>
+        <v>3.986413202725106e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006081940583640467</v>
+        <v>0.006313804877191808</v>
       </c>
       <c r="H9" t="n">
-        <v>2533.633433102007</v>
+        <v>4103.134057180736</v>
       </c>
       <c r="I9" t="n">
-        <v>1.061189560412292</v>
+        <v>1.124707419586817</v>
       </c>
       <c r="J9" t="n">
-        <v>-1279.812727665148</v>
+        <v>-1252.124164546048</v>
       </c>
       <c r="K9" t="n">
-        <v>-1271.303881944293</v>
+        <v>-1246.483601414838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I, X_calc, V_calc, mu_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.8199159914848282</v>
+        <v>-2.849347129365368</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005171315006113971</v>
+        <v>0.008848446608771311</v>
       </c>
       <c r="F10" t="n">
-        <v>3.817198277093439e-05</v>
+        <v>8.201166640333293e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006178347899797679</v>
+        <v>0.009056029284588965</v>
       </c>
       <c r="H10" t="n">
-        <v>2550.0729112243</v>
+        <v>4655.938609692626</v>
       </c>
       <c r="I10" t="n">
-        <v>1.097003035666776</v>
+        <v>2.311723093952186</v>
       </c>
       <c r="J10" t="n">
-        <v>-1271.849502092121</v>
+        <v>-1162.672481903456</v>
       </c>
       <c r="K10" t="n">
-        <v>-1257.668092557363</v>
+        <v>-1157.031918772246</v>
       </c>
     </row>
   </sheetData>
